--- a/Packages/cn.etetet.yiuilubangen/Luban/Config/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.yiuilubangen/Luban/Config/Base/__tables__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="14055"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>##var</t>
   </si>
@@ -108,9 +108,6 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
-  </si>
-  <si>
-    <t>AI</t>
   </si>
   <si>
     <t>Unit</t>
@@ -1055,8 +1052,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
   <cols>
     <col min="2" max="2" width="12.375" customWidth="1"/>
     <col min="3" max="3" width="34.25" customWidth="1"/>
@@ -1162,45 +1159,21 @@
       </c>
       <c r="C4" t="str">
         <f>_xlfn.CONCAT(B4,"ConfigCategory")</f>
-        <v>AIConfigCategory</v>
+        <v>UnitConfigCategory</v>
       </c>
       <c r="D4" t="str">
         <f>_xlfn.CONCAT(B4,"Config")</f>
-        <v>AIConfig</v>
+        <v>UnitConfig</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
       <c r="F4" t="str">
         <f>_xlfn.CONCAT(B4,".xlsx")</f>
-        <v>AI.xlsx</v>
+        <v>Unit.xlsx</v>
       </c>
       <c r="L4" t="str">
         <f>_xlfn.CONCAT(B4,"ConfigCategory")</f>
-        <v>AIConfigCategory</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" spans="2:12">
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="str">
-        <f>_xlfn.CONCAT(B5,"ConfigCategory")</f>
-        <v>UnitConfigCategory</v>
-      </c>
-      <c r="D5" t="str">
-        <f>_xlfn.CONCAT(B5,"Config")</f>
-        <v>UnitConfig</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" t="str">
-        <f>_xlfn.CONCAT(B5,".xlsx")</f>
-        <v>Unit.xlsx</v>
-      </c>
-      <c r="L5" t="str">
-        <f>_xlfn.CONCAT(B5,"ConfigCategory")</f>
         <v>UnitConfigCategory</v>
       </c>
     </row>
